--- a/artfynd/A 30058-2024 artfynd.xlsx
+++ b/artfynd/A 30058-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445048</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445066</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445071</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445056</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445061</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1339,6 +1369,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445047</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1451,6 +1486,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445051</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1563,6 +1603,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445063</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1675,6 +1720,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445075</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1784,6 +1834,11 @@
       <c r="AY11" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445043</t>
         </is>
       </c>
     </row>
@@ -1901,6 +1956,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445045</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2012,6 +2072,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445042</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2123,6 +2188,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445044</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2234,6 +2304,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445055</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2345,6 +2420,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445060</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2456,6 +2536,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445065</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2567,6 +2652,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445068</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2688,6 +2778,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445049</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2804,6 +2899,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445057</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2920,6 +3020,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445059</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3036,6 +3141,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445069</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3152,6 +3262,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445072</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3268,6 +3383,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445073</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3384,6 +3504,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445074</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3500,6 +3625,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445076</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3616,6 +3746,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445079</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3732,6 +3867,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445070</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3843,6 +3983,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445052</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3954,6 +4099,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445058</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4065,8 +4215,45 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445067</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 30058-2024 artfynd.xlsx
+++ b/artfynd/A 30058-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135445048</v>
       </c>
       <c r="B2" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135445066</v>
       </c>
       <c r="B3" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135445071</v>
       </c>
       <c r="B4" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135445056</v>
       </c>
       <c r="B5" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135445061</v>
       </c>
       <c r="B6" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135445047</v>
       </c>
       <c r="B7" t="n">
-        <v>101376</v>
+        <v>101424</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>135445051</v>
       </c>
       <c r="B8" t="n">
-        <v>101376</v>
+        <v>101424</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>135445063</v>
       </c>
       <c r="B9" t="n">
-        <v>101376</v>
+        <v>101424</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>135445075</v>
       </c>
       <c r="B10" t="n">
-        <v>101376</v>
+        <v>101424</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>135445043</v>
       </c>
       <c r="B11" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>135445045</v>
       </c>
       <c r="B12" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>135445042</v>
       </c>
       <c r="B13" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>135445044</v>
       </c>
       <c r="B14" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>135445055</v>
       </c>
       <c r="B15" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>135445060</v>
       </c>
       <c r="B16" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>135445065</v>
       </c>
       <c r="B17" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>135445068</v>
       </c>
       <c r="B18" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>135445049</v>
       </c>
       <c r="B19" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>135445057</v>
       </c>
       <c r="B20" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>135445059</v>
       </c>
       <c r="B21" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>135445069</v>
       </c>
       <c r="B22" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>135445072</v>
       </c>
       <c r="B23" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>135445073</v>
       </c>
       <c r="B24" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
         <v>135445074</v>
       </c>
       <c r="B25" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>135445076</v>
       </c>
       <c r="B26" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>135445079</v>
       </c>
       <c r="B27" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>135445070</v>
       </c>
       <c r="B28" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>135445052</v>
       </c>
       <c r="B29" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>135445058</v>
       </c>
       <c r="B30" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4110,7 +4110,7 @@
         <v>135445067</v>
       </c>
       <c r="B31" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 30058-2024 artfynd.xlsx
+++ b/artfynd/A 30058-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135445048</v>
       </c>
       <c r="B2" t="n">
-        <v>97479</v>
+        <v>97506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135445066</v>
       </c>
       <c r="B3" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135445071</v>
       </c>
       <c r="B4" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135445056</v>
       </c>
       <c r="B5" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135445061</v>
       </c>
       <c r="B6" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135445047</v>
       </c>
       <c r="B7" t="n">
-        <v>101424</v>
+        <v>101451</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>135445051</v>
       </c>
       <c r="B8" t="n">
-        <v>101424</v>
+        <v>101451</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>135445063</v>
       </c>
       <c r="B9" t="n">
-        <v>101424</v>
+        <v>101451</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>135445075</v>
       </c>
       <c r="B10" t="n">
-        <v>101424</v>
+        <v>101451</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>135445043</v>
       </c>
       <c r="B11" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>135445045</v>
       </c>
       <c r="B12" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>135445042</v>
       </c>
       <c r="B13" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>135445044</v>
       </c>
       <c r="B14" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>135445055</v>
       </c>
       <c r="B15" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>135445060</v>
       </c>
       <c r="B16" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>135445065</v>
       </c>
       <c r="B17" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>135445068</v>
       </c>
       <c r="B18" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>135445052</v>
       </c>
       <c r="B29" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>135445058</v>
       </c>
       <c r="B30" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4110,7 +4110,7 @@
         <v>135445067</v>
       </c>
       <c r="B31" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 30058-2024 artfynd.xlsx
+++ b/artfynd/A 30058-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135445048</v>
       </c>
       <c r="B2" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135445066</v>
       </c>
       <c r="B3" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135445071</v>
       </c>
       <c r="B4" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135445056</v>
       </c>
       <c r="B5" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135445047</v>
       </c>
       <c r="B7" t="n">
-        <v>101456</v>
+        <v>101458</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>135445051</v>
       </c>
       <c r="B8" t="n">
-        <v>101456</v>
+        <v>101458</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>135445063</v>
       </c>
       <c r="B9" t="n">
-        <v>101456</v>
+        <v>101458</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>135445075</v>
       </c>
       <c r="B10" t="n">
-        <v>101456</v>
+        <v>101458</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>135445043</v>
       </c>
       <c r="B11" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>135445045</v>
       </c>
       <c r="B12" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>135445052</v>
       </c>
       <c r="B29" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>135445058</v>
       </c>
       <c r="B30" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4110,7 +4110,7 @@
         <v>135445067</v>
       </c>
       <c r="B31" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 30058-2024 artfynd.xlsx
+++ b/artfynd/A 30058-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135445048</v>
       </c>
       <c r="B2" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135445066</v>
       </c>
       <c r="B3" t="n">
-        <v>92046</v>
+        <v>92060</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135445071</v>
       </c>
       <c r="B4" t="n">
-        <v>92046</v>
+        <v>92060</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135445056</v>
       </c>
       <c r="B5" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135445061</v>
       </c>
       <c r="B6" t="n">
-        <v>83292</v>
+        <v>83294</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135445047</v>
       </c>
       <c r="B7" t="n">
-        <v>101458</v>
+        <v>101475</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>135445051</v>
       </c>
       <c r="B8" t="n">
-        <v>101458</v>
+        <v>101475</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>135445063</v>
       </c>
       <c r="B9" t="n">
-        <v>101458</v>
+        <v>101475</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>135445075</v>
       </c>
       <c r="B10" t="n">
-        <v>101458</v>
+        <v>101475</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>135445043</v>
       </c>
       <c r="B11" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>135445045</v>
       </c>
       <c r="B12" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>135445042</v>
       </c>
       <c r="B13" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>135445044</v>
       </c>
       <c r="B14" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>135445055</v>
       </c>
       <c r="B15" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>135445060</v>
       </c>
       <c r="B16" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>135445065</v>
       </c>
       <c r="B17" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>135445068</v>
       </c>
       <c r="B18" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>135445049</v>
       </c>
       <c r="B19" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>135445057</v>
       </c>
       <c r="B20" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>135445059</v>
       </c>
       <c r="B21" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>135445069</v>
       </c>
       <c r="B22" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>135445072</v>
       </c>
       <c r="B23" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>135445073</v>
       </c>
       <c r="B24" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
         <v>135445074</v>
       </c>
       <c r="B25" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>135445076</v>
       </c>
       <c r="B26" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>135445079</v>
       </c>
       <c r="B27" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>135445070</v>
       </c>
       <c r="B28" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>135445052</v>
       </c>
       <c r="B29" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>135445058</v>
       </c>
       <c r="B30" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4110,7 +4110,7 @@
         <v>135445067</v>
       </c>
       <c r="B31" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
